--- a/feedback_surveys/020_net_user_feedback_survey--feedback_surveys.xlsx
+++ b/feedback_surveys/020_net_user_feedback_survey--feedback_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -987,8 +987,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="39" customWidth="1" min="2" max="2"/>
-    <col width="39" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1016,12 +1016,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'very_dissatisfied'}</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Very Dissatisfied'}</t>
+          <t>Very Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1033,12 +1033,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_dissatisfied'}</t>
+          <t>somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Dissatisfied'}</t>
+          <t>Somewhat Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1050,12 +1050,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1067,12 +1067,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_satisfied'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Satisfied'}</t>
+          <t>Somewhat Satisfied</t>
         </is>
       </c>
     </row>
@@ -1084,12 +1084,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'very_satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Very Satisfied'}</t>
+          <t>Very Satisfied</t>
         </is>
       </c>
     </row>
@@ -1101,12 +1101,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'website_navigation'}</t>
+          <t>website_navigation</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Website Navigation'}</t>
+          <t>Website Navigation</t>
         </is>
       </c>
     </row>
@@ -1118,12 +1118,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'search_functionality'}</t>
+          <t>search_functionality</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Search Functionality'}</t>
+          <t>Search Functionality</t>
         </is>
       </c>
     </row>
@@ -1135,12 +1135,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'search_results_display'}</t>
+          <t>search_results_display</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Search Results Display'}</t>
+          <t>Search Results Display</t>
         </is>
       </c>
     </row>
@@ -1152,12 +1152,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'search_help'}</t>
+          <t>search_help</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Search Help'}</t>
+          <t>Search Help</t>
         </is>
       </c>
     </row>
@@ -1169,12 +1169,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1203,12 +1203,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1220,12 +1220,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1271,12 +1271,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -1305,12 +1305,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'occasionally'}</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Occasionally'}</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
@@ -1322,12 +1322,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'often'}</t>
+          <t>often</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Often'}</t>
+          <t>Often</t>
         </is>
       </c>
     </row>
@@ -1339,12 +1339,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'always'}</t>
+          <t>always</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Always'}</t>
+          <t>Always</t>
         </is>
       </c>
     </row>
@@ -1356,12 +1356,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'1-5'}</t>
+          <t>1-5</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': '1-5'}</t>
+          <t>1-5</t>
         </is>
       </c>
     </row>
@@ -1373,12 +1373,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'6-10'}</t>
+          <t>6-10</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': '6-10'}</t>
+          <t>6-10</t>
         </is>
       </c>
     </row>
@@ -1390,12 +1390,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'11-15'}</t>
+          <t>11-15</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': '11-15'}</t>
+          <t>11-15</t>
         </is>
       </c>
     </row>
@@ -1407,12 +1407,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'16+'}</t>
+          <t>16+</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': '16+'}</t>
+          <t>16+</t>
         </is>
       </c>
     </row>
@@ -1424,12 +1424,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'technical_issues'}</t>
+          <t>technical_issues</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'Technical Issues'}</t>
+          <t>Technical Issues</t>
         </is>
       </c>
     </row>
@@ -1441,12 +1441,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'content_issues'}</t>
+          <t>content_issues</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'Content Issues'}</t>
+          <t>Content Issues</t>
         </is>
       </c>
     </row>
@@ -1458,12 +1458,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'design_issues'}</t>
+          <t>design_issues</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 'Design Issues'}</t>
+          <t>Design Issues</t>
         </is>
       </c>
     </row>
@@ -1475,12 +1475,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1492,12 +1492,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_'user_error'}</t>
+          <t>user_error</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': 'User Error'}</t>
+          <t>User Error</t>
         </is>
       </c>
     </row>
@@ -1509,12 +1509,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'label':_'network_service_provider'}</t>
+          <t>network_service_provider</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'label': 'Network Service Provider'}</t>
+          <t>Network Service Provider</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
